--- a/Result/profitability/3492.xlsx
+++ b/Result/profitability/3492.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.27375</v>
+        <v>0.2475000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>29.07625</v>
+        <v>28.4025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32125</v>
+        <v>0.30625</v>
       </c>
       <c r="N3" t="n">
-        <v>27.77</v>
+        <v>27.2425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.1950000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>26.1275</v>
+        <v>25.45375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2662500000000001</v>
+        <v>0.2412500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>26.01375</v>
+        <v>25.08625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2150000000000001</v>
+        <v>0.1612500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>24.6075</v>
+        <v>23.985</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08250000000000007</v>
+        <v>0.09125000000000005</v>
       </c>
       <c r="N7" t="n">
-        <v>23.37</v>
+        <v>23.25</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8433,6 +8433,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>236</v>
+      </c>
+      <c r="D64" t="n">
+        <v>174</v>
+      </c>
+      <c r="E64" t="n">
+        <v>62</v>
+      </c>
+      <c r="F64" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="G64" t="n">
+        <v>12</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>13</v>
+      </c>
+      <c r="K64" t="n">
+        <v>7</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.3800000000000001</v>
+      </c>
+      <c r="N64" t="n">
+        <v>30.07125</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-0.3225806451612904</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-1.969999999999999</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.06973451327433622</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-0.4878048780487805</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-7.420000000000002</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-0.2201780415430268</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
